--- a/Portfolio Performance.xlsx
+++ b/Portfolio Performance.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2380A57-D9D7-44C7-A8C0-C38275E0805E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDDB8319-CE2D-49C8-BCBE-93FB1E5A0897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Positions" sheetId="2" r:id="rId1"/>
@@ -56,7 +56,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="6">
+  <futureMetadata name="XLRICHVALUE" count="7">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -99,13 +99,20 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="24"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
   <cellMetadata count="1">
     <bk>
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="6">
+  <valueMetadata count="7">
     <bk>
       <rc t="2" v="0"/>
     </bk>
@@ -124,12 +131,15 @@
     <bk>
       <rc t="2" v="5"/>
     </bk>
+    <bk>
+      <rc t="2" v="6"/>
+    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="69">
   <si>
     <t>Positions</t>
   </si>
@@ -334,6 +344,9 @@
   <si>
     <t>USD</t>
   </si>
+  <si>
+    <t>CHGG</t>
+  </si>
 </sst>
 </file>
 
@@ -438,7 +451,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -455,22 +468,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FFBFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -566,33 +568,14 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <font>
-        <color rgb="FFB0432F"/>
-        <name val="Arial"/>
-        <charset val="1"/>
-      </font>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <font>
         <color rgb="FFB0432F"/>
@@ -1156,10 +1139,10 @@
                 <c:formatCode>\$#,##0.00;"($"#,##0.00\);\-</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>1154.0571280747999</c:v>
+                  <c:v>1408.56284164</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4128.5229727199994</c:v>
+                  <c:v>4213.16875196</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -1171,7 +1154,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1560.12</c:v>
+                  <c:v>1558.65</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0</c:v>
@@ -1402,7 +1385,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="22">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="25">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a23hqh&amp;q=ARCX%3aSPY&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -1422,26 +1405,29 @@
     <v>779.37</v>
     <v>629.28</v>
     <v>0.99880000000000002</v>
-    <v>8.3800000000000008</v>
-    <v>1.1113E-2</v>
+    <v>11.82</v>
+    <v>-3.1839999999999999E-4</v>
+    <v>1.5518000000000001E-2</v>
+    <v>-0.24629999999999999</v>
     <v>USD</v>
     <v>NYSE Arca</v>
     <v>ARCX</v>
     <v>9.4499999999999998E-4</v>
-    <v>763.41</v>
+    <v>774.89</v>
     <v>ETF</v>
-    <v>46282.715024675781</v>
+    <v>46286.879783865625</v>
     <v>0</v>
-    <v>759.96</v>
+    <v>766.03</v>
     <v>811937033817.45996</v>
     <v>State Street SPDR S&amp;P500</v>
-    <v>763.4</v>
-    <v>754.05</v>
-    <v>762.43</v>
+    <v>766.25099999999998</v>
+    <v>761.69</v>
+    <v>773.51</v>
+    <v>773.25369999999998</v>
     <v>SPY</v>
     <v>State Street SPDR S&amp;P500 (ARCX:SPY)</v>
-    <v>19749554</v>
-    <v>37300271</v>
+    <v>49688909</v>
+    <v>39222092</v>
   </rv>
   <rv s="2">
     <v>1</v>
@@ -1465,26 +1451,29 @@
     <v>748.65</v>
     <v>555.6</v>
     <v>1.0137</v>
-    <v>12.11</v>
-    <v>1.7183999999999998E-2</v>
+    <v>20.771000000000001</v>
+    <v>-4.395E-4</v>
+    <v>2.8820999999999999E-2</v>
+    <v>-0.32590000000000002</v>
     <v>USD</v>
     <v>Nasdaq Stock Market</v>
     <v>XNAS</v>
     <v>1.8E-3</v>
-    <v>717.16</v>
+    <v>743.22</v>
     <v>ETF</v>
-    <v>46282.715019455471</v>
+    <v>46286.879859062501</v>
     <v>3</v>
-    <v>713.32</v>
+    <v>727.81</v>
     <v>488981000838.15997</v>
     <v>Invesco QQQ Trust 1</v>
-    <v>716.11</v>
-    <v>704.72</v>
-    <v>716.83</v>
+    <v>727.89</v>
+    <v>720.69899999999996</v>
+    <v>741.47</v>
+    <v>741.14409999999998</v>
     <v>QQQ</v>
     <v>Invesco QQQ Trust 1 (XNAS:QQQ)</v>
-    <v>17116724</v>
-    <v>30840596</v>
+    <v>46315000</v>
+    <v>31843928</v>
   </rv>
   <rv s="2">
     <v>4</v>
@@ -1508,26 +1497,29 @@
     <v>101.8</v>
     <v>86.84</v>
     <v>0.99909999999999999</v>
-    <v>0.52</v>
-    <v>5.5630000000000002E-3</v>
+    <v>0.91</v>
+    <v>0</v>
+    <v>9.7940000000000006E-3</v>
+    <v>0</v>
     <v>USD</v>
     <v>NYSE Arca</v>
     <v>ARCX</v>
     <v>1.2999999999999999E-3</v>
-    <v>94.27</v>
+    <v>93.95</v>
     <v>ETF</v>
-    <v>46282.714883772656</v>
+    <v>46286.871847395312</v>
     <v>6</v>
-    <v>93.61</v>
+    <v>93.25</v>
     <v>38085772930</v>
     <v>Vanguard RE;ETF</v>
-    <v>94.22</v>
-    <v>93.48</v>
-    <v>94</v>
+    <v>93.27</v>
+    <v>92.91</v>
+    <v>93.82</v>
+    <v>93.81</v>
     <v>VNQ</v>
     <v>Vanguard RE;ETF (ARCX:VNQ)</v>
-    <v>1442128</v>
-    <v>3016729</v>
+    <v>3017329</v>
+    <v>3061325</v>
   </rv>
   <rv s="2">
     <v>7</v>
@@ -1550,34 +1542,37 @@
     <v>8</v>
     <v>1292.6500000000001</v>
     <v>712.05</v>
-    <v>0.45860000000000001</v>
-    <v>6.61</v>
-    <v>5.8089999999999999E-3</v>
+    <v>0.45400000000000001</v>
+    <v>11.86</v>
+    <v>5.3220000000000003E-4</v>
+    <v>1.0286999999999999E-2</v>
+    <v>0.62</v>
     <v>USD</v>
-    <v>Eli Lilly and Company is a medicine company which discovers, develops, manufactures, and markets products in a single business segment called human pharmaceutical products. The Company manufactures and distributes its products through facilities in the United States, including Puerto Rico, and in Europe and Asia. Its Cardiometabolic Health products include Basaglar; Humalog, Humalog Mix 75/25, Humalog U-100, Humalog U-200, Humalog Mix 50/50, insulin lispro, and others; Humulin, and others; Jardiance; Mounjaro; Trulicity; Zepbound, and others. Its oncology products include Cyramza, Erbitux, Tyvyt, Verzenio, Retevmo, Jaypirca, and others. Its immunology products include Ebglyss, Olumiant, Omvoh, and Taltz. Its neuroscience products include Emgality and Kisunla. Its LillyDirect, a direct-to-patient digital health care platform, provides delivery of select Lilly medicines dispensed by third-party pharmacies to patients. The Company’s products are sold in approximately 90 countries.</v>
+    <v>Eli Lilly and Company is a medicine company, which discovers, develops, manufactures, and market products in a single business segment called human pharmaceutical products. The Company manufacture and distribute its products through facilities in the United States, including Puerto Rico, and in Europe and Asia. The Company’s products are sold in approximately 90 countries. Its Cardiometabolic Health products Basaglar; Humalog, Humalog Mix 75/25, Humalog U-100, Humalog U-200, Humalog Mix 50/50, insulin lispro, and others; Humulin, Humulin 70/30, and others; Jardiance; Mounjaro; Trulicity; Zepbound, and others. Its oncology products include Cyramza, Erbitux, Tyvyt, Verzenio, Retevmo, Jaypirca, and others. Its immunology products include Ebglyss, Olumiant, Omvoh, and Taltz. Its neuroscience products include Emgality and Kisunla. Its LillyDirect, a direct-to-patient digital health care platform, provides delivery of select Lilly medicines dispensed by third-party pharmacies to patients.</v>
     <v>50000</v>
     <v>New York Stock Exchange</v>
     <v>XNYS</v>
     <v>XNYS</v>
     <v>Lilly Corporate Ctr, Drop Code 1094, INDIANAPOLIS, IN, 46285 US</v>
-    <v>1159.75</v>
+    <v>1170.8998999999999</v>
     <v>Pharmaceuticals</v>
     <v>Stock</v>
-    <v>46282.714994733593</v>
+    <v>46286.879807140627</v>
     <v>9</v>
-    <v>1138.26</v>
-    <v>1077317305953</v>
+    <v>1134.4100000000001</v>
+    <v>1096483336509</v>
     <v>ELI LILLY AND COMPANY</v>
     <v>ELI LILLY AND COMPANY</v>
-    <v>1149.3399999999999</v>
-    <v>38.4086</v>
-    <v>1137.82</v>
-    <v>1144.43</v>
+    <v>1144.4949999999999</v>
+    <v>39.091900000000003</v>
+    <v>1152.93</v>
+    <v>1164.79</v>
+    <v>1165.51</v>
     <v>941357100</v>
     <v>LLY</v>
     <v>ELI LILLY AND COMPANY (XNYS:LLY)</v>
-    <v>632224</v>
-    <v>2348314</v>
+    <v>2228509</v>
+    <v>2451487</v>
     <v>1901</v>
   </rv>
   <rv s="2">
@@ -1619,11 +1614,13 @@
     <v>12</v>
     <v>Finance</v>
     <v>8</v>
-    <v>370.86</v>
+    <v>368.73</v>
     <v>190.12</v>
-    <v>1.4188000000000001</v>
-    <v>-0.2437</v>
-    <v>-9.7290000000000007E-4</v>
+    <v>1.4114</v>
+    <v>0.6</v>
+    <v>-4.8090000000000003E-4</v>
+    <v>2.4099999999999998E-3</v>
+    <v>-0.12</v>
     <v>USD</v>
     <v>Adobe Inc. is a global technology company. The Company's Solutions enable digital experiences, starting with the first creative spark, to the creation and development of all content and media, to the personalized delivery across every channel. Its segments include Digital Media, Digital Experience, and Publishing and Advertising. The Digital Media segment provides products and services that allow individuals, teams, businesses, and enterprises to create, publish, and promote content, and to work with documents and creative content across different workflows. The Digital Experience segment provides an integrated platform set of products, services and solutions that enable businesses to create, manage, execute, measure, monetize &amp; optimize customer experiences. The Publishing and Advertising segment contains legacy products and services that address diverse market opportunities, including eLearning solutions, technical document publishing, web conferencing, document and forms platforms.</v>
     <v>31360</v>
@@ -1631,25 +1628,26 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>345 Park Avenue, SAN JOSE, CA, 95110-2704 US</v>
-    <v>251.99</v>
+    <v>251.48</v>
     <v>15</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46282.715032534375</v>
+    <v>46286.878391816404</v>
     <v>16</v>
-    <v>245.40100000000001</v>
-    <v>99476879250</v>
+    <v>244.23</v>
+    <v>99184200000</v>
     <v>ADOBE INC.</v>
     <v>ADOBE INC.</v>
-    <v>250.05</v>
-    <v>13.965</v>
-    <v>250.5</v>
-    <v>250.25630000000001</v>
+    <v>248.92</v>
+    <v>13.9239</v>
+    <v>248.92</v>
+    <v>249.52</v>
+    <v>249.4</v>
     <v>397500000</v>
     <v>ADBE</v>
     <v>ADOBE INC. (XNAS:ADBE)</v>
-    <v>2208297</v>
-    <v>4945270</v>
+    <v>4986694</v>
+    <v>5182242</v>
     <v>1997</v>
   </rv>
   <rv s="2">
@@ -1673,9 +1671,11 @@
     <v>8</v>
     <v>101.99</v>
     <v>65.41</v>
-    <v>1.2628999999999999</v>
-    <v>-0.1</v>
-    <v>-1.4089999999999999E-3</v>
+    <v>1.2614000000000001</v>
+    <v>0.32</v>
+    <v>1.2700000000000001E-3</v>
+    <v>4.5390000000000005E-3</v>
+    <v>0.09</v>
     <v>USD</v>
     <v>Uber Technologies, Inc. operates a technology platform that uses network and technology to power movement from point A to point B. It develops and operates technology applications supporting a variety of offerings on its platform (platform(s)). Its segments include Mobility, Delivery and Freight. Mobility products connect consumers with drivers who provide rides in a variety of vehicles, such as cars, auto rickshaws, motorbikes, minibuses, or taxis. Delivery offerings allow consumers to search for and discover local restaurants, order a meal, and either pick-up at the restaurant or have the meal delivered. In certain markets, the Delivery segment provides offerings for grocery, alcohol, and convenience store delivery as well as select other goods. The Freight segment connects carriers with shippers on its platform, and gives carriers upfront, pricing and the ability to book a shipment. The Freight segment also includes transportation management and other logistics service offerings.</v>
     <v>34000</v>
@@ -1683,34 +1683,88 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>1725 3Rd Street, SAN FRANCISCO, CA, 94158 US</v>
-    <v>71.641000000000005</v>
+    <v>71.39</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46282.714998969532</v>
+    <v>46286.879239212503</v>
     <v>19</v>
-    <v>70.239999999999995</v>
-    <v>144756227200</v>
+    <v>70.110799999999998</v>
+    <v>144654099200</v>
     <v>UBER TECHNOLOGIES, INC.</v>
     <v>UBER TECHNOLOGIES, INC.</v>
-    <v>71.424999999999997</v>
-    <v>15.556699999999999</v>
-    <v>70.97</v>
-    <v>70.87</v>
+    <v>70.819999999999993</v>
+    <v>15.5457</v>
+    <v>70.5</v>
+    <v>70.819999999999993</v>
+    <v>70.930000000000007</v>
     <v>2042560000</v>
     <v>UBER</v>
     <v>UBER TECHNOLOGIES, INC. (XNYS:UBER)</v>
-    <v>8823081</v>
-    <v>16979144</v>
+    <v>16633797</v>
+    <v>17300322</v>
     <v>2010</v>
   </rv>
   <rv s="2">
     <v>20</v>
   </rv>
+  <rv s="0">
+    <v>https://www.bing.com/financeapi/forcetrigger?t=a1plyc&amp;q=XNYS%3aCHGG&amp;form=skydnc</v>
+    <v>Learn more on Bing</v>
+  </rv>
+  <rv s="7">
+    <v>en-US</v>
+    <v>a1plyc</v>
+    <v>268435456</v>
+    <v>1</v>
+    <v>Powered by Refinitiv</v>
+    <v>14</v>
+    <v>CHEGG, INC. (XNYS:CHGG)</v>
+    <v>6</v>
+    <v>15</v>
+    <v>Finance</v>
+    <v>16</v>
+    <v>1.9</v>
+    <v>0.45</v>
+    <v>2.1684000000000001</v>
+    <v>2.4500000000000001E-2</v>
+    <v>5.6940000000000003E-3</v>
+    <v>3.5226E-2</v>
+    <v>4.1000000000000003E-3</v>
+    <v>USD</v>
+    <v>Chegg, Inc. provides a student-first connected learning platform. The Company provides individualized learning support to students as they pursue their educational journeys. Available on demand 24/7 and powered by quality learning insights, the Chegg platform offers students artificial intelligence (AI)-powered academic support thoughtfully designed for education, coupled with access to a vast network of subject matter experts who help ensure quality and accuracy. Its service and product offerings fall into two categories: Subscription Services, which encompass its Chegg Study Pack, Chegg Study, Chegg Writing, Chegg Math, and Busuu offerings that can be accessed internationally through its websites and on mobile devices, and Skills and Other, which include its Chegg Skills, advertising services, content licensing, print textbooks and eTextbooks offerings. Chegg Study subscribers have access to personalized, step-by-step learning support powered by AI and computational engines.</v>
+    <v>564</v>
+    <v>New York Stock Exchange</v>
+    <v>XNYS</v>
+    <v>XNYS</v>
+    <v>3990 Freedom Cir, SANTA CLARA, CA, 95054 US</v>
+    <v>0.72440000000000004</v>
+    <v>Professional &amp; Commercial Services</v>
+    <v>Stock</v>
+    <v>46286.849501863282</v>
+    <v>22</v>
+    <v>0.69689999999999996</v>
+    <v>79939800</v>
+    <v>CHEGG, INC.</v>
+    <v>CHEGG, INC.</v>
+    <v>0.72</v>
+    <v>0.69550000000000001</v>
+    <v>0.72</v>
+    <v>0.72409999999999997</v>
+    <v>111027500</v>
+    <v>CHGG</v>
+    <v>CHEGG, INC. (XNYS:CHGG)</v>
+    <v>595889</v>
+    <v>1270537</v>
+    <v>2005</v>
+  </rv>
+  <rv s="2">
+    <v>23</v>
+  </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="7">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="8">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -1731,7 +1785,9 @@
     <k n="52 week low"/>
     <k n="Beta"/>
     <k n="Change"/>
+    <k n="Change % (Extended hours)"/>
     <k n="Change (%)"/>
+    <k n="Change (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Exchange" t="s"/>
     <k n="Exchange abbreviation" t="s"/>
@@ -1746,6 +1802,7 @@
     <k n="Open"/>
     <k n="Previous close"/>
     <k n="Price"/>
+    <k n="Price (Extended hours)"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
     <k n="Volume"/>
@@ -1770,7 +1827,9 @@
     <k n="52 week low"/>
     <k n="Beta"/>
     <k n="Change"/>
+    <k n="Change % (Extended hours)"/>
     <k n="Change (%)"/>
+    <k n="Change (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -1791,6 +1850,7 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
+    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -1826,7 +1886,9 @@
     <k n="52 week low"/>
     <k n="Beta"/>
     <k n="Change"/>
+    <k n="Change % (Extended hours)"/>
     <k n="Change (%)"/>
+    <k n="Change (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -1848,6 +1910,53 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
+    <k n="Price (Extended hours)"/>
+    <k n="Shares outstanding"/>
+    <k n="Ticker symbol" t="s"/>
+    <k n="UniqueName" t="s"/>
+    <k n="Volume"/>
+    <k n="Volume average"/>
+    <k n="Year incorporated"/>
+  </s>
+  <s t="_linkedentitycore">
+    <k n="%EntityCulture" t="s"/>
+    <k n="%EntityId" t="s"/>
+    <k n="%EntityServiceId"/>
+    <k n="%IsRefreshable" t="b"/>
+    <k n="%ProviderInfo" t="s"/>
+    <k n="_Display" t="spb"/>
+    <k n="_DisplayString" t="s"/>
+    <k n="_Flags" t="spb"/>
+    <k n="_Format" t="spb"/>
+    <k n="_Icon" t="s"/>
+    <k n="_SubLabel" t="spb"/>
+    <k n="52 week high"/>
+    <k n="52 week low"/>
+    <k n="Beta"/>
+    <k n="Change"/>
+    <k n="Change % (Extended hours)"/>
+    <k n="Change (%)"/>
+    <k n="Change (Extended hours)"/>
+    <k n="Currency" t="s"/>
+    <k n="Description" t="s"/>
+    <k n="Employees"/>
+    <k n="Exchange" t="s"/>
+    <k n="Exchange abbreviation" t="s"/>
+    <k n="ExchangeID" t="s"/>
+    <k n="Headquarters" t="s"/>
+    <k n="High"/>
+    <k n="Industry" t="s"/>
+    <k n="Instrument type" t="s"/>
+    <k n="Last trade time"/>
+    <k n="LearnMoreOnLink" t="r"/>
+    <k n="Low"/>
+    <k n="Market cap"/>
+    <k n="Name" t="s"/>
+    <k n="Official name" t="s"/>
+    <k n="Open"/>
+    <k n="Previous close"/>
+    <k n="Price"/>
+    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -1860,8 +1969,8 @@
 
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
-  <spbArrays count="3">
-    <a count="34">
+  <spbArrays count="4">
+    <a count="37">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -1872,13 +1981,16 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
+      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
+      <v t="s">Change (Extended hours)</v>
       <v t="s">Expense ratio</v>
       <v t="s">Change (%)</v>
+      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -1897,7 +2009,7 @@
       <v t="s">LearnMoreOnLink</v>
       <v t="s">%ProviderInfo</v>
     </a>
-    <a count="42">
+    <a count="45">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -1908,13 +2020,16 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
+      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
+      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
+      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -1941,7 +2056,7 @@
       <v t="s">ExchangeID</v>
       <v t="s">%ProviderInfo</v>
     </a>
-    <a count="43">
+    <a count="46">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -1952,13 +2067,16 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
+      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
+      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
+      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -1986,8 +2104,54 @@
       <v t="s">ExchangeID</v>
       <v t="s">%ProviderInfo</v>
     </a>
+    <a count="44">
+      <v t="s">%EntityServiceId</v>
+      <v t="s">_Format</v>
+      <v t="s">%IsRefreshable</v>
+      <v t="s">%EntityCulture</v>
+      <v t="s">%EntityId</v>
+      <v t="s">_Icon</v>
+      <v t="s">_Display</v>
+      <v t="s">Name</v>
+      <v t="s">_SubLabel</v>
+      <v t="s">Price</v>
+      <v t="s">Price (Extended hours)</v>
+      <v t="s">Exchange</v>
+      <v t="s">Official name</v>
+      <v t="s">Last trade time</v>
+      <v t="s">Ticker symbol</v>
+      <v t="s">Exchange abbreviation</v>
+      <v t="s">Change</v>
+      <v t="s">Change (Extended hours)</v>
+      <v t="s">Change (%)</v>
+      <v t="s">Change % (Extended hours)</v>
+      <v t="s">Currency</v>
+      <v t="s">Previous close</v>
+      <v t="s">Open</v>
+      <v t="s">High</v>
+      <v t="s">Low</v>
+      <v t="s">52 week high</v>
+      <v t="s">52 week low</v>
+      <v t="s">Volume</v>
+      <v t="s">Volume average</v>
+      <v t="s">Market cap</v>
+      <v t="s">Beta</v>
+      <v t="s">Shares outstanding</v>
+      <v t="s">Description</v>
+      <v t="s">Employees</v>
+      <v t="s">Headquarters</v>
+      <v t="s">Industry</v>
+      <v t="s">Instrument type</v>
+      <v t="s">Year incorporated</v>
+      <v t="s">_Flags</v>
+      <v t="s">UniqueName</v>
+      <v t="s">_DisplayString</v>
+      <v t="s">LearnMoreOnLink</v>
+      <v t="s">ExchangeID</v>
+      <v t="s">%ProviderInfo</v>
+    </a>
   </spbArrays>
-  <spbData count="14">
+  <spbData count="17">
     <spb s="0">
       <v>0</v>
       <v>Name</v>
@@ -2021,13 +2185,19 @@
       <v>4</v>
       <v>7</v>
       <v>8</v>
+      <v>1</v>
+      <v>1</v>
+      <v>5</v>
     </spb>
     <spb s="4">
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>at close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>from previous close</v>
       <v>GMT</v>
+      <v>Real-Time Nasdaq Last Sale</v>
+      <v>from close</v>
+      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -2061,13 +2231,19 @@
       <v>9</v>
       <v>8</v>
       <v>4</v>
+      <v>1</v>
+      <v>1</v>
+      <v>5</v>
     </spb>
     <spb s="7">
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
+      <v>Real-Time Nasdaq Last Sale</v>
+      <v>from close</v>
+      <v>from close</v>
     </spb>
     <spb s="0">
       <v>2</v>
@@ -2107,16 +2283,58 @@
       <v>9</v>
       <v>8</v>
       <v>4</v>
+      <v>1</v>
+      <v>1</v>
+      <v>5</v>
     </spb>
     <spb s="11">
       <v>Powered by Refinitiv</v>
+    </spb>
+    <spb s="0">
+      <v>3</v>
+      <v>Name</v>
+      <v>LearnMoreOnLink</v>
+    </spb>
+    <spb s="12">
+      <v>1</v>
+      <v>2</v>
+      <v>1</v>
+      <v>3</v>
+      <v>1</v>
+      <v>1</v>
+      <v>1</v>
+      <v>4</v>
+      <v>4</v>
+      <v>5</v>
+      <v>6</v>
+      <v>1</v>
+      <v>1</v>
+      <v>1</v>
+      <v>4</v>
+      <v>7</v>
+      <v>9</v>
+      <v>8</v>
+      <v>4</v>
+      <v>1</v>
+      <v>1</v>
+      <v>5</v>
+    </spb>
+    <spb s="7">
+      <v>at close</v>
+      <v>from previous close</v>
+      <v>from previous close</v>
+      <v>Source: Nasdaq</v>
+      <v>GMT</v>
+      <v>Delayed 15 minutes</v>
+      <v>from close</v>
+      <v>from close</v>
     </spb>
   </spbData>
 </supportingPropertyBags>
 </file>
 
 <file path=xl/richData/rdsupportingpropertybagstructure.xml><?xml version="1.0" encoding="utf-8"?>
-<spbStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="12">
+<spbStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="13">
   <s>
     <k n="^Order" t="spba"/>
     <k n="TitleProperty" t="s"/>
@@ -2150,6 +2368,9 @@
     <k n="Volume average" t="i"/>
     <k n="Last trade time" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
+    <k n="Price (Extended hours)" t="i"/>
+    <k n="Change (Extended hours)" t="i"/>
+    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -2157,6 +2378,9 @@
     <k n="Exchange" t="s"/>
     <k n="Change (%)" t="s"/>
     <k n="Last trade time" t="s"/>
+    <k n="Price (Extended hours)" t="s"/>
+    <k n="Change (Extended hours)" t="s"/>
+    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="ExchangeID" t="spb"/>
@@ -2185,6 +2409,9 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
+    <k n="Price (Extended hours)" t="i"/>
+    <k n="Change (Extended hours)" t="i"/>
+    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -2192,6 +2419,9 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
+    <k n="Price (Extended hours)" t="s"/>
+    <k n="Change (Extended hours)" t="s"/>
+    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="ShowInDotNotation" t="b"/>
@@ -2226,9 +2456,36 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
+    <k n="Price (Extended hours)" t="i"/>
+    <k n="Change (Extended hours)" t="i"/>
+    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="name" t="s"/>
+  </s>
+  <s>
+    <k n="Low" t="i"/>
+    <k n="Beta" t="i"/>
+    <k n="High" t="i"/>
+    <k n="Name" t="i"/>
+    <k n="Open" t="i"/>
+    <k n="Price" t="i"/>
+    <k n="Change" t="i"/>
+    <k n="Volume" t="i"/>
+    <k n="Employees" t="i"/>
+    <k n="Change (%)" t="i"/>
+    <k n="Market cap" t="i"/>
+    <k n="52 week low" t="i"/>
+    <k n="52 week high" t="i"/>
+    <k n="Previous close" t="i"/>
+    <k n="Volume average" t="i"/>
+    <k n="Last trade time" t="i"/>
+    <k n="Year incorporated" t="i"/>
+    <k n="`%EntityServiceId" t="i"/>
+    <k n="Shares outstanding" t="i"/>
+    <k n="Price (Extended hours)" t="i"/>
+    <k n="Change (Extended hours)" t="i"/>
+    <k n="Change % (Extended hours)" t="i"/>
   </s>
 </spbStructures>
 </file>
@@ -2520,7 +2777,7 @@
       </c>
       <c r="C1" s="23">
         <f ca="1">TODAY()</f>
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -2589,7 +2846,7 @@
       </c>
       <c r="E3" s="34" cm="1">
         <f t="array" aca="1" ref="E3" ca="1">_FV(A3,"Price")</f>
-        <v>762.43</v>
+        <v>773.51</v>
       </c>
       <c r="F3" s="25">
         <v>2.2848039999999998</v>
@@ -2606,23 +2863,23 @@
       </c>
       <c r="J3" s="34">
         <f ca="1">IF(A3="","",F3*E3)</f>
-        <v>1742.0031137199996</v>
+        <v>1767.31874204</v>
       </c>
       <c r="K3" s="27">
         <f ca="1">IF(A3="","",J3-H3)</f>
-        <v>-21.637093880000066</v>
+        <v>3.6785344400002487</v>
       </c>
       <c r="L3" s="28">
         <f ca="1">IF(OR(A3="",H3=0),"",K3/H3)</f>
-        <v>-1.2268428552921403E-2</v>
+        <v>2.085762404456677E-3</v>
       </c>
       <c r="M3" s="28">
         <f ca="1">IF(OR(A3="",H3=0),"",(K3+I3)/H3)</f>
-        <v>-1.0357607975414853E-2</v>
+        <v>3.9965829819632254E-3</v>
       </c>
       <c r="N3" s="28">
         <f ca="1">IF(OR(A3="",$J$12=0),"",J3/$J$12)</f>
-        <v>0.25457832260070273</v>
+        <v>0.24613159050143546</v>
       </c>
       <c r="O3" s="29"/>
       <c r="P3" s="29"/>
@@ -2644,7 +2901,7 @@
       </c>
       <c r="E4" s="34" cm="1">
         <f t="array" aca="1" ref="E4" ca="1">_FV(A4,"Price")</f>
-        <v>716.83</v>
+        <v>741.47</v>
       </c>
       <c r="F4" s="25">
         <v>2.4565000000000001</v>
@@ -2662,23 +2919,23 @@
       </c>
       <c r="J4" s="34">
         <f t="shared" ref="J4:J11" ca="1" si="1">IF(B4="","",F4*E4)</f>
-        <v>1760.8928950000002</v>
+        <v>1821.4210550000003</v>
       </c>
       <c r="K4" s="27">
         <f t="shared" ref="K4:K11" ca="1" si="2">IF(B4="","",J4-H4)</f>
-        <v>59.32447500000012</v>
+        <v>119.85263500000019</v>
       </c>
       <c r="L4" s="28">
         <f t="shared" ref="L4:L11" ca="1" si="3">IF(OR(B4="",H4=0),"",K4/H4)</f>
-        <v>3.4864583934861769E-2</v>
+        <v>7.04365652249236E-2</v>
       </c>
       <c r="M4" s="28">
         <f t="shared" ref="M4:M11" ca="1" si="4">IF(OR(B4="",H4=0),"",(K4+I4)/H4)</f>
-        <v>3.5781385152881554E-2</v>
+        <v>7.1353366442943378E-2</v>
       </c>
       <c r="N4" s="28">
-        <f ca="1">IF(OR(B4="",$J$12=0),"",J4/$J$12)</f>
-        <v>0.25733889678950961</v>
+        <f t="shared" ref="N4:N11" ca="1" si="5">IF(OR(B4="",$J$12=0),"",J4/$J$12)</f>
+        <v>0.25366633113530684</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
@@ -2697,7 +2954,7 @@
       </c>
       <c r="E5" s="34" cm="1">
         <f t="array" aca="1" ref="E5" ca="1">_FV(A5,"Price")</f>
-        <v>94</v>
+        <v>93.82</v>
       </c>
       <c r="F5" s="25">
         <v>6.6556059999999997</v>
@@ -2714,23 +2971,23 @@
       </c>
       <c r="J5" s="34">
         <f t="shared" ca="1" si="1"/>
-        <v>625.62696399999993</v>
+        <v>624.42895491999991</v>
       </c>
       <c r="K5" s="27">
         <f t="shared" ca="1" si="2"/>
-        <v>-25.291302800000039</v>
+        <v>-26.489311880000059</v>
       </c>
       <c r="L5" s="28">
         <f t="shared" ca="1" si="3"/>
-        <v>-3.8854805725971435E-2</v>
+        <v>-4.0695296523517478E-2</v>
       </c>
       <c r="M5" s="28">
         <f t="shared" ca="1" si="4"/>
-        <v>-3.7441417829326834E-2</v>
+        <v>-3.928190862687287E-2</v>
       </c>
       <c r="N5" s="28">
-        <f ca="1">IF(OR(B5="",$J$12=0),"",J5/$J$12)</f>
-        <v>9.1429838336380034E-2</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>8.6963199208878295E-2</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
@@ -2749,7 +3006,7 @@
       </c>
       <c r="E6" s="34" cm="1">
         <f t="array" aca="1" ref="E6" ca="1">_FV(A6,"Price")</f>
-        <v>1144.43</v>
+        <v>1164.79</v>
       </c>
       <c r="F6" s="25">
         <v>0.204902</v>
@@ -2766,23 +3023,23 @@
       </c>
       <c r="J6" s="34">
         <f t="shared" ca="1" si="1"/>
-        <v>234.49599586000002</v>
+        <v>238.66780058000001</v>
       </c>
       <c r="K6" s="27">
         <f t="shared" ca="1" si="2"/>
-        <v>56.725069680000018</v>
+        <v>60.896874400000002</v>
       </c>
       <c r="L6" s="28">
         <f t="shared" ca="1" si="3"/>
-        <v>0.31909081478578599</v>
+        <v>0.34255812077133208</v>
       </c>
       <c r="M6" s="28">
         <f t="shared" ca="1" si="4"/>
-        <v>0.32567231843849992</v>
+        <v>0.349139624424046</v>
       </c>
       <c r="N6" s="28">
-        <f ca="1">IF(OR(B6="",$J$12=0),"",J6/$J$12)</f>
-        <v>3.4269512386311159E-2</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>3.3238874211466526E-2</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
@@ -2801,7 +3058,7 @@
       </c>
       <c r="E7" s="34" cm="1">
         <f t="array" aca="1" ref="E7" ca="1">_FV(A7,"Price")</f>
-        <v>250.25630000000001</v>
+        <v>249.52</v>
       </c>
       <c r="F7" s="25">
         <v>1.817496</v>
@@ -2818,23 +3075,23 @@
       </c>
       <c r="J7" s="34">
         <f t="shared" ca="1" si="1"/>
-        <v>454.8398242248</v>
+        <v>453.50160192000004</v>
       </c>
       <c r="K7" s="27">
         <f t="shared" ca="1" si="2"/>
-        <v>-45.153325375200041</v>
+        <v>-46.491547679999996</v>
       </c>
       <c r="L7" s="28">
         <f t="shared" ca="1" si="3"/>
-        <v>-9.0307888040712547E-2</v>
+        <v>-9.2984369320247173E-2</v>
       </c>
       <c r="M7" s="28">
         <f t="shared" ca="1" si="4"/>
-        <v>-9.0307888040712547E-2</v>
+        <v>-9.2984369320247173E-2</v>
       </c>
       <c r="N7" s="28">
-        <f ca="1">IF(OR(B7="",$J$12=0),"",J7/$J$12)</f>
-        <v>6.6470810867769722E-2</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>6.3158426332691558E-2</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -2853,7 +3110,7 @@
       </c>
       <c r="E8" s="34" cm="1">
         <f t="array" aca="1" ref="E8" ca="1">_FV(A8,"Price")</f>
-        <v>70.87</v>
+        <v>70.819999999999993</v>
       </c>
       <c r="F8" s="25">
         <v>6.5573769999999998</v>
@@ -2870,40 +3127,76 @@
       </c>
       <c r="J8" s="34">
         <f t="shared" ca="1" si="1"/>
-        <v>464.72130799000001</v>
+        <v>464.39343913999994</v>
       </c>
       <c r="K8" s="27">
         <f t="shared" ca="1" si="2"/>
-        <v>-35.278688259999967</v>
+        <v>-35.60655711000004</v>
       </c>
       <c r="L8" s="28">
         <f t="shared" ca="1" si="3"/>
-        <v>-7.0557377049180262E-2</v>
+        <v>-7.1213114754098444E-2</v>
       </c>
       <c r="M8" s="28">
         <f t="shared" ca="1" si="4"/>
-        <v>-7.0557377049180262E-2</v>
+        <v>-7.1213114754098444E-2</v>
       </c>
       <c r="N8" s="28">
-        <f ca="1">IF(OR(B8="",$J$12=0),"",J8/$J$12)</f>
-        <v>6.7914902179626618E-2</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>6.4675314687163962E-2</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" s="22"/>
-      <c r="B9" s="30"/>
-      <c r="C9" s="33"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="25"/>
-      <c r="G9" s="26"/>
-      <c r="H9" s="34"/>
-      <c r="I9" s="31"/>
-      <c r="J9" s="34"/>
-      <c r="K9" s="27"/>
-      <c r="L9" s="28"/>
-      <c r="M9" s="28"/>
-      <c r="N9" s="28"/>
+      <c r="A9" s="22" t="e" vm="7">
+        <v>#VALUE!</v>
+      </c>
+      <c r="B9" s="43" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="C9" ca="1">_FV(A9,"Name")</f>
+        <v>CHEGG, INC.</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="34" cm="1">
+        <f t="array" aca="1" ref="E9" ca="1">_FV(A9,"Price")</f>
+        <v>0.72</v>
+      </c>
+      <c r="F9" s="25">
+        <v>350</v>
+      </c>
+      <c r="G9" s="26">
+        <v>0.71550000000000002</v>
+      </c>
+      <c r="H9" s="34">
+        <f t="shared" ref="H9" si="6">IF(B9="","",F9*G9)</f>
+        <v>250.42500000000001</v>
+      </c>
+      <c r="I9" s="31">
+        <v>0</v>
+      </c>
+      <c r="J9" s="34">
+        <f t="shared" ref="J9" ca="1" si="7">IF(B9="","",F9*E9)</f>
+        <v>252</v>
+      </c>
+      <c r="K9" s="27">
+        <f t="shared" ref="K9" ca="1" si="8">IF(B9="","",J9-H9)</f>
+        <v>1.5749999999999886</v>
+      </c>
+      <c r="L9" s="28">
+        <f t="shared" ref="L9" ca="1" si="9">IF(OR(B9="",H9=0),"",K9/H9)</f>
+        <v>6.2893081761005833E-3</v>
+      </c>
+      <c r="M9" s="28">
+        <f t="shared" ref="M9" ca="1" si="10">IF(OR(B9="",H9=0),"",(K9+I9)/H9)</f>
+        <v>6.2893081761005833E-3</v>
+      </c>
+      <c r="N9" s="28">
+        <f t="shared" ca="1" si="5"/>
+        <v>3.5095627817971681E-2</v>
+      </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
@@ -2923,35 +3216,35 @@
         <v>1</v>
       </c>
       <c r="F10" s="25">
-        <v>1560.12</v>
+        <v>1558.65</v>
       </c>
       <c r="G10" s="26">
         <v>1</v>
       </c>
       <c r="H10" s="34">
-        <f t="shared" ref="H10" si="5">IF(B10="","",F10*G10)</f>
-        <v>1560.12</v>
+        <f t="shared" ref="H10" si="11">IF(B10="","",F10*G10)</f>
+        <v>1558.65</v>
       </c>
       <c r="I10" s="31"/>
       <c r="J10" s="34">
-        <f t="shared" ref="J10" si="6">IF(B10="","",F10*E10)</f>
-        <v>1560.12</v>
+        <f t="shared" ref="J10" si="12">IF(B10="","",F10*E10)</f>
+        <v>1558.65</v>
       </c>
       <c r="K10" s="27">
-        <f t="shared" ref="K10" si="7">IF(B10="","",J10-H10)</f>
+        <f t="shared" ref="K10" si="13">IF(B10="","",J10-H10)</f>
         <v>0</v>
       </c>
       <c r="L10" s="28">
-        <f t="shared" ref="L10" si="8">IF(OR(B10="",H10=0),"",K10/H10)</f>
+        <f t="shared" ref="L10" si="14">IF(OR(B10="",H10=0),"",K10/H10)</f>
         <v>0</v>
       </c>
       <c r="M10" s="28">
-        <f t="shared" ref="M10" si="9">IF(OR(B10="",H10=0),"",(K10+I10)/H10)</f>
+        <f t="shared" ref="M10" si="15">IF(OR(B10="",H10=0),"",(K10+I10)/H10)</f>
         <v>0</v>
       </c>
       <c r="N10" s="28">
-        <f ca="1">IF(OR(B10="",$J$12=0),"",J10/$J$12)</f>
-        <v>0.22799771683970005</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>0.21707063610508556</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
@@ -2983,7 +3276,7 @@
         <v/>
       </c>
       <c r="N11" s="28" t="str">
-        <f ca="1">IF(OR(B11="",$J$12=0),"",J11/$J$12)</f>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
@@ -2998,7 +3291,7 @@
       <c r="G12" s="6"/>
       <c r="H12" s="7">
         <f>SUM(H3:H11)</f>
-        <v>6854.0109664299998</v>
+        <v>7102.9659664299998</v>
       </c>
       <c r="I12" s="7">
         <f>SUM(I3:I11)</f>
@@ -3006,31 +3299,31 @@
       </c>
       <c r="J12" s="7">
         <f ca="1">SUM(J3:J11)</f>
-        <v>6842.7001007948002</v>
+        <v>7180.381593600001</v>
       </c>
       <c r="K12" s="7">
         <f ca="1">J12-H12</f>
-        <v>-11.310865635199661</v>
+        <v>77.415627170001244</v>
       </c>
       <c r="L12" s="8">
         <f ca="1">IF(H12=0,"",K12/H12)</f>
-        <v>-1.6502549661211109E-3</v>
+        <v>1.0899056469632908E-2</v>
       </c>
       <c r="M12" s="8">
         <f ca="1">IF(H12=0,"",(K12+I12)/H12)</f>
-        <v>-6.260371709668587E-4</v>
+        <v>1.1887376001667536E-2</v>
       </c>
       <c r="N12" s="8">
         <f ca="1">IF(J12=0,"",SUM(N3:N11))</f>
-        <v>1</v>
+        <v>0.99999999999999989</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="K3:M12">
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3039,7 +3332,7 @@
       <formula1>"Stock,ETF,Mutual Fund,Bond,Crypto,Cash,Other"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" error="Enter a number of zero or more." sqref="E11 F3:F4 G3:I11 F7:F11" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" error="Enter a number of zero or more." sqref="E11 F3:F4 F7:F11 G3:I11" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -3089,7 +3382,7 @@
       </c>
       <c r="B4" s="11">
         <f ca="1">Positions!J12</f>
-        <v>6842.7001007948002</v>
+        <v>7180.381593600001</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -3100,7 +3393,7 @@
       </c>
       <c r="B5" s="13">
         <f>Positions!H12</f>
-        <v>6854.0109664299998</v>
+        <v>7102.9659664299998</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
@@ -3111,7 +3404,7 @@
       </c>
       <c r="B6" s="11">
         <f ca="1">Positions!K12</f>
-        <v>-11.310865635199661</v>
+        <v>77.415627170001244</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -3122,7 +3415,7 @@
       </c>
       <c r="B7" s="14">
         <f ca="1">Positions!L12</f>
-        <v>-1.6502549661211109E-3</v>
+        <v>1.0899056469632908E-2</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -3144,7 +3437,7 @@
       </c>
       <c r="B9" s="15">
         <f ca="1">Positions!M12</f>
-        <v>-6.260371709668587E-4</v>
+        <v>1.1887376001667536E-2</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -3155,7 +3448,7 @@
       </c>
       <c r="B10" s="16">
         <f>COUNTA(Positions!$B$3:$B$11)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -3177,7 +3470,7 @@
       </c>
       <c r="B12" s="14">
         <f ca="1">IF(COUNT(Positions!$N$3:$N$11)=0,"",MAX(Positions!$N$3:$N$11))</f>
-        <v>0.25733889678950961</v>
+        <v>0.25366633113530684</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
@@ -3199,7 +3492,7 @@
       </c>
       <c r="B14" s="14">
         <f ca="1">IF(COUNT(Positions!$M$3:$M$11)=0,"",MAX(Positions!$M$3:$M$11))</f>
-        <v>0.32567231843849992</v>
+        <v>0.349139624424046</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -3221,7 +3514,7 @@
       </c>
       <c r="B16" s="14">
         <f ca="1">IF(COUNT(Positions!$M$3:$M$11)=0,"",MIN(Positions!$M$3:$M$11))</f>
-        <v>-9.0307888040712547E-2</v>
+        <v>-9.2984369320247173E-2</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
@@ -3260,15 +3553,15 @@
       </c>
       <c r="B20" s="19">
         <f ca="1">SUMIF(Positions!$D$3:$D$11,A20,Positions!$J$3:$J$11)</f>
-        <v>1154.0571280747999</v>
+        <v>1408.56284164</v>
       </c>
       <c r="C20" s="20">
         <f t="shared" ref="C20:C26" ca="1" si="0">IF($B$27=0,"",B20/$B$27)</f>
-        <v>0.16865522543370751</v>
+        <v>0.19616824304929378</v>
       </c>
       <c r="D20" s="21">
         <f>COUNTIF(Positions!$D$3:$D$11,A20)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -3277,11 +3570,11 @@
       </c>
       <c r="B21" s="19">
         <f ca="1">SUMIF(Positions!$D$3:$D$11,A21,Positions!$J$3:$J$11)</f>
-        <v>4128.5229727199994</v>
+        <v>4213.16875196</v>
       </c>
       <c r="C21" s="20">
         <f t="shared" ca="1" si="0"/>
-        <v>0.60334705772659236</v>
+        <v>0.58676112084562071</v>
       </c>
       <c r="D21" s="21">
         <f>COUNTIF(Positions!$D$3:$D$11,A21)</f>
@@ -3345,11 +3638,11 @@
       </c>
       <c r="B25" s="19">
         <f>SUMIF(Positions!$D$3:$D$11,A25,Positions!$J$3:$J$11)</f>
-        <v>1560.12</v>
+        <v>1558.65</v>
       </c>
       <c r="C25" s="20">
         <f t="shared" ca="1" si="0"/>
-        <v>0.22799771683970008</v>
+        <v>0.21707063610508562</v>
       </c>
       <c r="D25" s="21">
         <f>COUNTIF(Positions!$D$3:$D$11,A25)</f>
@@ -3379,15 +3672,15 @@
       </c>
       <c r="B27" s="7">
         <f ca="1">SUM(B20:B26)</f>
-        <v>6842.7001007947993</v>
+        <v>7180.3815935999992</v>
       </c>
       <c r="C27" s="8">
         <f ca="1">IF(B27=0,"",SUM(C20:C26))</f>
-        <v>0.99999999999999989</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="D27" s="6">
         <f>SUM(D20:D26)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -3398,10 +3691,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B6:B9">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3413,7 +3706,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2D10F30-3DFC-4EFD-A968-C0359B0A229A}">
-  <dimension ref="A1:O499"/>
+  <dimension ref="A1:O498"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -3507,7 +3800,7 @@
         <v>SPY</v>
       </c>
       <c r="J4" s="40">
-        <f t="shared" ref="J4:J10" si="0">IF(I4="","",SUMIF($B$4:$B$499,I4,$D$4:$D$499))</f>
+        <f t="shared" ref="J4:J10" si="0">IF(I4="","",SUMIF($B$4:$B$498,I4,$D$4:$D$498))</f>
         <v>2.2848039999999998</v>
       </c>
       <c r="K4" s="41">
@@ -3515,19 +3808,19 @@
         <v>2.2848039999999998</v>
       </c>
       <c r="L4" s="27">
-        <f t="shared" ref="L4:L10" si="1">IF(I4="","",ROUND(J4-K4,6))</f>
+        <f t="shared" ref="L4:L9" si="1">IF(I4="","",ROUND(J4-K4,6))</f>
         <v>0</v>
       </c>
       <c r="M4" s="27">
-        <f t="shared" ref="M4:M10" si="2">IF($I4="","",SUMIFS($F$4:$F$499,$B$4:$B$499,$I4,$C$4:$C$499,"Buy"))</f>
+        <f t="shared" ref="M4:M11" si="2">IF($I4="","",SUMIFS($F$4:$F$498,$B$4:$B$498,$I4,$C$4:$C$498,"Buy"))</f>
         <v>2199.9899999999998</v>
       </c>
       <c r="N4" s="27">
-        <f t="shared" ref="N4:N10" si="3">IF($I4="","",SUMIFS($F$4:$F$499,$B$4:$B$499,$I4,$C$4:$C$499,"Dividend"))</f>
+        <f t="shared" ref="N4:N11" si="3">IF($I4="","",SUMIFS($F$4:$F$498,$B$4:$B$498,$I4,$C$4:$C$498,"Dividend"))</f>
         <v>3.37</v>
       </c>
       <c r="O4" s="27">
-        <f t="shared" ref="O4:O10" si="4">IF($I4="","",SUMIFS($F$4:$F$499,$B$4:$B$499,$I4,$C$4:$C$499,"Sell"))</f>
+        <f t="shared" ref="O4:O11" si="4">IF($I4="","",SUMIFS($F$4:$F$498,$B$4:$B$498,$I4,$C$4:$C$498,"Sell"))</f>
         <v>500</v>
       </c>
     </row>
@@ -3791,23 +4084,23 @@
       </c>
       <c r="G10" s="35"/>
       <c r="I10" s="42" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J10" s="40">
-        <f t="shared" ref="J10" si="5">IF(I10="","",SUMIF($B$4:$B$499,I10,$D$4:$D$499))</f>
-        <v>1560.12</v>
+        <f t="shared" si="0"/>
+        <v>700</v>
       </c>
       <c r="K10" s="41">
         <f>IF(I10="","",INDEX(Positions!$F$3:$F$11,MATCH(I10,Positions!$B$3:$B$11,0)))</f>
-        <v>1560.12</v>
+        <v>350</v>
       </c>
       <c r="L10" s="27">
-        <f t="shared" ref="L10" si="6">IF(I10="","",ROUND(J10-K10,6))</f>
-        <v>0</v>
+        <f t="shared" ref="L10" si="5">IF(I10="","",ROUND(J10-K10,6))</f>
+        <v>350</v>
       </c>
       <c r="M10" s="27">
         <f t="shared" si="2"/>
-        <v>1560.12</v>
+        <v>250.95</v>
       </c>
       <c r="N10" s="27">
         <f t="shared" si="3"/>
@@ -3815,7 +4108,7 @@
       </c>
       <c r="O10" s="27">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>249.48</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
@@ -3838,23 +4131,31 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="G11" s="35"/>
-      <c r="I11" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
-      <c r="M11" s="7">
-        <f>SUM(M4:M10)</f>
-        <v>7286.71</v>
-      </c>
-      <c r="N11" s="7">
-        <f>SUM(N4:N10)</f>
-        <v>7.02</v>
-      </c>
-      <c r="O11" s="7">
-        <f>SUM(O4:O10)</f>
-        <v>500</v>
+      <c r="I11" s="42" t="s">
+        <v>67</v>
+      </c>
+      <c r="J11" s="40">
+        <v>1558.65</v>
+      </c>
+      <c r="K11" s="41">
+        <f>IF(I11="","",INDEX(Positions!$F$3:$F$11,MATCH(I11,Positions!$B$3:$B$11,0)))</f>
+        <v>1558.65</v>
+      </c>
+      <c r="L11" s="27">
+        <f t="shared" ref="L11" si="6">IF(I11="","",ROUND(J11-K11,6))</f>
+        <v>0</v>
+      </c>
+      <c r="M11" s="27">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N11" s="27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O11" s="27">
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
@@ -3877,6 +4178,24 @@
         <v>50</v>
       </c>
       <c r="G12" s="35"/>
+      <c r="I12" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
+      <c r="M12" s="7">
+        <f>SUM(M4:M11)</f>
+        <v>5977.54</v>
+      </c>
+      <c r="N12" s="7">
+        <f>SUM(N4:N11)</f>
+        <v>7.02</v>
+      </c>
+      <c r="O12" s="7">
+        <f>SUM(O4:O11)</f>
+        <v>749.48</v>
+      </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="39">
@@ -5124,33 +5443,45 @@
       <c r="G75" s="35"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="43">
-        <v>46282</v>
-      </c>
-      <c r="B76" s="44" t="s">
-        <v>67</v>
-      </c>
-      <c r="C76" s="44" t="s">
+      <c r="A76" s="39">
+        <v>46286</v>
+      </c>
+      <c r="B76" s="38" t="s">
+        <v>68</v>
+      </c>
+      <c r="C76" s="38" t="s">
         <v>48</v>
       </c>
-      <c r="D76" s="45">
-        <v>1560.12</v>
-      </c>
-      <c r="E76" s="46">
-        <v>1</v>
-      </c>
-      <c r="F76" s="46">
-        <v>1560.12</v>
-      </c>
-      <c r="G76" s="47"/>
+      <c r="D76" s="37">
+        <v>350</v>
+      </c>
+      <c r="E76" s="36">
+        <v>0.71699999999999997</v>
+      </c>
+      <c r="F76" s="36">
+        <v>250.95</v>
+      </c>
+      <c r="G76" s="35"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="39"/>
-      <c r="B77" s="38"/>
-      <c r="C77" s="38"/>
-      <c r="D77" s="37"/>
-      <c r="E77" s="36"/>
-      <c r="F77" s="36"/>
+      <c r="A77" s="39">
+        <v>46286</v>
+      </c>
+      <c r="B77" s="38" t="s">
+        <v>68</v>
+      </c>
+      <c r="C77" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="D77" s="37">
+        <v>350</v>
+      </c>
+      <c r="E77" s="36">
+        <v>0.71299999999999997</v>
+      </c>
+      <c r="F77" s="36">
+        <v>249.48</v>
+      </c>
       <c r="G77" s="35"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -8942,19 +9273,10 @@
       <c r="F498" s="36"/>
       <c r="G498" s="35"/>
     </row>
-    <row r="499" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A499" s="39"/>
-      <c r="B499" s="38"/>
-      <c r="C499" s="38"/>
-      <c r="D499" s="37"/>
-      <c r="E499" s="36"/>
-      <c r="F499" s="36"/>
-      <c r="G499" s="35"/>
-    </row>
   </sheetData>
   <autoFilter ref="A3:G75" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" error="Choose Buy, Sell, Dividend, Dividend Reinvest, or Stock Lending." sqref="C4:C499" xr:uid="{00000000-0002-0000-0200-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" error="Choose Buy, Sell, Dividend, Dividend Reinvest, or Stock Lending." sqref="C4:C498" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"Buy,Sell,Dividend,Dividend Reinvest,Stock Lending"</formula1>
     </dataValidation>
   </dataValidations>
